--- a/xls/square_16_tri3_12.xlsx
+++ b/xls/square_16_tri3_12.xlsx
@@ -482,13 +482,13 @@
         <v>864</v>
       </c>
       <c r="I12">
-        <v>1.99098262058083</v>
+        <v>1.9909826916734188</v>
       </c>
       <c r="J12">
-        <v>-0.9725244012309998</v>
+        <v>-0.9725243300956822</v>
       </c>
       <c r="K12">
-        <v>0.13547530863239113</v>
+        <v>0.1354754007891401</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -517,13 +517,13 @@
         <v>1014</v>
       </c>
       <c r="I13">
-        <v>-2.1963383287954774</v>
+        <v>-2.1963383965073753</v>
       </c>
       <c r="J13">
-        <v>-2.07191210555199</v>
+        <v>-2.0719119454469865</v>
       </c>
       <c r="K13">
-        <v>-1.4020042036906861</v>
+        <v>-1.4020042605881395</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -552,13 +552,13 @@
         <v>1176</v>
       </c>
       <c r="I14">
-        <v>-2.1828362093327502</v>
+        <v>-2.1828360089739163</v>
       </c>
       <c r="J14">
-        <v>-2.0850156128160164</v>
+        <v>-2.0850155211752135</v>
       </c>
       <c r="K14">
-        <v>-1.4861145756653236</v>
+        <v>-1.4861147589608965</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -587,13 +587,13 @@
         <v>1350</v>
       </c>
       <c r="I15">
-        <v>-2.1829588527844255</v>
+        <v>-2.1829591511017843</v>
       </c>
       <c r="J15">
-        <v>-2.0331720361100354</v>
+        <v>-2.033172136345328</v>
       </c>
       <c r="K15">
-        <v>-1.0272508424235924</v>
+        <v>-1.0272506033265643</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -622,13 +622,13 @@
         <v>1536</v>
       </c>
       <c r="I16">
-        <v>-2.1612138245388732</v>
+        <v>-2.1612140031123617</v>
       </c>
       <c r="J16">
-        <v>-1.8883516854522806</v>
+        <v>-1.8883517927205984</v>
       </c>
       <c r="K16">
-        <v>-0.7408667348366677</v>
+        <v>-0.7408667702407062</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -657,13 +657,13 @@
         <v>1734</v>
       </c>
       <c r="I17">
-        <v>-2.132404973160438</v>
+        <v>-2.132404749469553</v>
       </c>
       <c r="J17">
-        <v>-1.872239505730461</v>
+        <v>-1.8722396459743331</v>
       </c>
       <c r="K17">
-        <v>1.4965094255551419</v>
+        <v>1.496511348611617</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -692,13 +692,13 @@
         <v>1944</v>
       </c>
       <c r="I18">
-        <v>-1.3300713925756915</v>
+        <v>-1.3300714811560364</v>
       </c>
       <c r="J18">
-        <v>-1.0017289179634632</v>
+        <v>-1.001728928299732</v>
       </c>
       <c r="K18">
-        <v>1.6752587936671517</v>
+        <v>1.675258779774728</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -727,13 +727,13 @@
         <v>2166</v>
       </c>
       <c r="I19">
-        <v>-0.04915154537608384</v>
+        <v>-0.049151544616414286</v>
       </c>
       <c r="J19">
-        <v>-0.051387724703615016</v>
+        <v>-0.051387723798271966</v>
       </c>
       <c r="K19">
-        <v>3.7403834260300473</v>
+        <v>3.7403834190620673</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -762,13 +762,13 @@
         <v>2400</v>
       </c>
       <c r="I20">
-        <v>-0.005577060476221559</v>
+        <v>-0.005577060480930863</v>
       </c>
       <c r="J20">
-        <v>-0.0052401680173461565</v>
+        <v>-0.00524016801530527</v>
       </c>
       <c r="K20">
-        <v>3.2911910140529677</v>
+        <v>3.2911910131755953</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -797,13 +797,13 @@
         <v>2646</v>
       </c>
       <c r="I21">
-        <v>-0.0022198186229227057</v>
+        <v>-0.0022198186241754376</v>
       </c>
       <c r="J21">
-        <v>-0.002081861109787052</v>
+        <v>-0.0020818611107962736</v>
       </c>
       <c r="K21">
-        <v>3.096606106117985</v>
+        <v>3.0966061063478048</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -832,13 +832,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>-0.00034811672479991273</v>
+        <v>-0.0003481167246479576</v>
       </c>
       <c r="J22">
-        <v>-0.0002662116015218073</v>
+        <v>-0.0002662116014254119</v>
       </c>
       <c r="K22">
-        <v>2.564030118408994</v>
+        <v>2.564030118603036</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -867,13 +867,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>1.715972622307889e-5</v>
+        <v>1.7159726223464604e-5</v>
       </c>
       <c r="J23">
         <v>4.030189339518453e-6</v>
       </c>
       <c r="K23">
-        <v>1.9628535507776013</v>
+        <v>1.9628535510266116</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -902,13 +902,13 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-4.2992805761855964e-5</v>
+        <v>-4.299280575876981e-5</v>
       </c>
       <c r="J24">
-        <v>-2.9866876713929683e-5</v>
+        <v>-2.9866876712483093e-5</v>
       </c>
       <c r="K24">
-        <v>2.0290676427560492</v>
+        <v>2.0290676425539353</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -937,13 +937,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>3.454032694140648e-7</v>
+        <v>3.454032695104975e-7</v>
       </c>
       <c r="J25">
-        <v>-3.621046358111246e-7</v>
+        <v>-3.62104635859341e-7</v>
       </c>
       <c r="K25">
-        <v>1.5241737004786324</v>
+        <v>1.5241737003756355</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -972,13 +972,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-7.983866051159665e-6</v>
+        <v>-7.983866050822145e-6</v>
       </c>
       <c r="J26">
-        <v>-6.633955028059505e-6</v>
+        <v>-6.633955028300591e-6</v>
       </c>
       <c r="K26">
-        <v>1.7937631414660726</v>
+        <v>1.793763141501837</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1007,13 +1007,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>-5.36877810042192e-7</v>
+        <v>-5.368778099939756e-7</v>
       </c>
       <c r="J27">
-        <v>-4.268698173196832e-7</v>
+        <v>-4.268698173678996e-7</v>
       </c>
       <c r="K27">
-        <v>1.2741577738380936</v>
+        <v>1.2741577740216212</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1042,13 +1042,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>-8.728661186960395e-7</v>
+        <v>-8.72866118744256e-7</v>
       </c>
       <c r="J28">
-        <v>-9.609599408076768e-7</v>
+        <v>-9.609599407594605e-7</v>
       </c>
       <c r="K28">
-        <v>1.4337732694288705</v>
+        <v>1.433773269477367</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1077,13 +1077,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>-3.352885225604977e-7</v>
+        <v>-3.3528852270514695e-7</v>
       </c>
       <c r="J29">
         <v>-3.027853585844258e-7</v>
       </c>
       <c r="K29">
-        <v>1.1539196012442359</v>
+        <v>1.1539196012891269</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1115,10 +1115,10 @@
         <v>-1.8783449713123536e-7</v>
       </c>
       <c r="J30">
-        <v>-1.8493401704614634e-7</v>
+        <v>-1.8493401709436274e-7</v>
       </c>
       <c r="K30">
-        <v>1.0764838434117503</v>
+        <v>1.0764838434774193</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1147,13 +1147,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>-4.994696085119058e-7</v>
+        <v>-4.994696086083387e-7</v>
       </c>
       <c r="J31">
-        <v>-4.570219989635555e-7</v>
+        <v>-4.570219992046376e-7</v>
       </c>
       <c r="K31">
-        <v>1.2396212445370944</v>
+        <v>1.2396212446938764</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1182,13 +1182,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-2.333139716122464e-7</v>
+        <v>-2.333139715158136e-7</v>
       </c>
       <c r="J32">
-        <v>-2.0444652857361853e-7</v>
+        <v>-2.044465288147005e-7</v>
       </c>
       <c r="K32">
-        <v>1.0690956979539614</v>
+        <v>1.0690956977621893</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_16_tri3_12.xlsx
+++ b/xls/square_16_tri3_12.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <v>169</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10">
+        <v>289</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10">
+        <v>121</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10">
+        <v>600</v>
+      </c>
+      <c r="I10">
+        <v>7.531992276183452</v>
+      </c>
+      <c r="J10">
+        <v>2.5469370208646307</v>
+      </c>
+      <c r="K10">
+        <v>3.061104784950621</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>169</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11">
+        <v>289</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11">
+        <v>144</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11">
+        <v>726</v>
+      </c>
+      <c r="I11">
+        <v>4.496914326683382</v>
+      </c>
+      <c r="J11">
+        <v>0.6981994593297303</v>
+      </c>
+      <c r="K11">
+        <v>1.5545033574393128</v>
+      </c>
+    </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>11</v>
